--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, сколько поручений, и предложил has_length(1) или сообщение</t>
+          <t>…указал, что по падению не понять, сколько поручений, и предложил has_length(1) или сообщение. Отличие от Д313.3: там проверки стоят до обработки повтора, здесь по падению не видно, сколько поручений</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Подсчёт" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,7 +437,7 @@
     <col width="30" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
     <col width="55" customWidth="1" min="5" max="5"/>
-    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -468,7 +468,7 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>0 или 1</t>
+          <t>Найден (1/0)</t>
         </is>
       </c>
     </row>
@@ -657,7 +657,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>…указал на отладочный вывод в консоль и предложил убрать его или заменить логом. Отличие от Д302.3–Д302.5: там речь о самих проверках ответа и БД</t>
+          <t>…указал на отладочный вывод в консоль, или предложил убрать его или заменить логом. Отличие от Д302.3–Д302.5: там речь о самих проверках ответа и БД</t>
         </is>
       </c>
     </row>
@@ -701,12 +701,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:22</t>
+          <t>test_900302_second_iis.py:23</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Текст ошибки «У клиента уже есть действующий ИИС» не проверяется</t>
+          <t>Текст ошибки «У клиента уже есть действующий ИИС» не проверяется. Комментарий оправдывает это тем, что текст на стендах разный, хотя кейс требует именно этот текст</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -728,12 +728,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:22</t>
+          <t>test_900302_second_iis.py:21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2 кейса не сделан: не проверено, что в БД у клиента по-прежнему один ИИС</t>
+          <t>Шаг 2 кейса не сделан: шаг «Проверить, что второй ИИС не открыт» (строка 21 — его заголовок) смотрит только ответ API, а не то, что в БД у клиента по-прежнему один ИИС</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -900,7 +900,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>…указал, что данные готовятся в обход сервиса, и предложил пополнение через API</t>
+          <t>…указал, что данные готовятся в обход сервиса, или предложил пополнение через API</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка пройдёт при любой ошибке, и предложил проверять 422. Отличие от Д304.3: там проверка текста ошибки. Отличие от Д304.4 и Д304.5: там проверки в БД после отказа</t>
+          <t>…понял, что проверка пройдёт при любой ошибке, или предложил проверять 422. Отличие от Д304.3: там проверка текста ошибки. Отличие от Д304.4 и Д304.5: там проверки в БД после отказа</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1035,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>…указал на логин и пароль сотрудника бэк-офиса в коде и предложил фикстуру, окружение или хранилище секретов</t>
+          <t>…указал на логин и пароль сотрудника бэк-офиса в коде, или предложил фикстуру, окружение или хранилище секретов</t>
         </is>
       </c>
     </row>
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>…понял, что запрос может вернуть чужое поручение, и предложил искать по id из ответа или хотя бы по договору. Отличие от Д305.2: там тест портит общие данные по умолчанию для следующих тестов</t>
+          <t>…понял, что запрос может вернуть чужое поручение, или предложил искать по id из ответа или хотя бы по договору. Отличие от Д305.2: там тест портит общие данные по умолчанию для следующих тестов</t>
         </is>
       </c>
     </row>
@@ -1457,17 +1457,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>test_900308_close_with_balance.py:33–34</t>
+          <t>test_900308_close_with_balance.py:34</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Текст ошибки проверяется раньше кода ответа: если договор закроется, тест упадёт с KeyError: 'errorMessage', и по падению не понять, что договор закрылся</t>
+          <t>Код ответа проверяется только после текста ошибки: если договор закроется, тест упадёт с KeyError: 'errorMessage', и по падению не понять, что договор закрылся</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>…понял, что из-за порядка проверок падение будет непонятным, и предложил сначала проверять код. Отличие от Д308.3: там неполная проверка текста</t>
+          <t>…понял, что из-за порядка проверок падение будет непонятным, или предложил сначала проверять код. Отличие от Д308.3: там неполная проверка текста</t>
         </is>
       </c>
     </row>
@@ -1656,7 +1656,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, что в истории, и предложил проверку по полям записи или сообщение</t>
+          <t>…указал, что по падению не понять, что в истории, или предложил проверку по полям записи или сообщение</t>
         </is>
       </c>
     </row>
@@ -1700,12 +1700,12 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:6–7</t>
+          <t>test_900310_login_lock.py:7</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Логин и пароль клиента стенда — константы в коде</t>
+          <t>Пароль клиента стенда — константа в коде</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>…указал, что имя топика зашито строкой, и предложил константу из Topics</t>
+          <t>…указал, что имя топика зашито строкой, или предложил константу из Topics</t>
         </is>
       </c>
     </row>
@@ -1872,7 +1872,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>…понял, что найденное событие может быть о другом клиенте, и предложил искать по логину или clientId своего клиента. Засчитываем и «упадёт при параллельном запуске», если причина — поиск без привязки к своему клиенту</t>
+          <t>…понял, что найденное событие может быть о другом клиенте, или предложил искать по логину или clientId своего клиента. Засчитываем и «упадёт при параллельном запуске», если причина — поиск без привязки к своему клиенту</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>…указал на отладочный print и предложил убрать его или заменить логом или вложением Allure. Засчитываем и упоминание длинного вывода «[KAFKA] события» у упавшего TK900312</t>
+          <t>…указал на отладочный print, или предложил убрать его или заменить логом или вложением Allure. Засчитываем и упоминание длинного вывода «[KAFKA] события» у упавшего TK900312</t>
         </is>
       </c>
     </row>
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>…понял, что последнее сообщение может быть чужим, и предложил искать по номеру договора и источнику CFT, или объяснил этим падение TK900312. Отличие от Д312.2: там пауза вместо ожидания</t>
+          <t>…понял, что последнее сообщение может быть чужим, или предложил искать по номеру договора и источнику CFT, или объяснил этим падение TK900312. Отличие от Д312.2: там пауза вместо ожидания</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>…указал, что проверка допускает неверный остаток, и предложил сравнивать с 1 000</t>
+          <t>…указал, что проверка допускает неверный остаток, или предложил сравнивать с 1 000</t>
         </is>
       </c>
     </row>
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:6, test_900313_duplicate_payment.py:19, test_900313_duplicate_payment.py:24</t>
+          <t>test_900313_duplicate_payment.py:6, test_900313_duplicate_payment.py:19</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:24, test_900313_duplicate_payment.py:26–28</t>
+          <t>test_900313_duplicate_payment.py:24, test_900313_duplicate_payment.py:27</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -2191,7 +2191,7 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3: не проверено, что в топике invest.money-orders по договору одно событие EXECUTED на 1 000 ₽. Если дубль зачислится второй раз, другие системы получат второе событие о зачислении</t>
+          <t>Шаг 3 (строка 26 — заголовок шага проверки): не проверено, что в топике invest.money-orders по договору одно событие EXECUTED на 1 000 ₽. Если дубль зачислится второй раз, другие системы получат второе событие о зачислении</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2223,7 +2223,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, сколько поручений, и предложил has_length(1) или сообщение. Отличие от Д313.3: там проверки стоят до обработки повтора, здесь по падению не видно, сколько поручений</t>
+          <t>…указал, что по падению не понять, сколько поручений, или предложил has_length(1) или сообщение. Отличие от Д313.3: там проверки стоят до обработки повтора, здесь по падению не видно, сколько поручений</t>
         </is>
       </c>
     </row>
@@ -2250,7 +2250,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>…указал, что имя топика зашито строкой, и предложил константу из Topics</t>
+          <t>…указал, что имя топика зашито строкой, или предложил константу из Topics</t>
         </is>
       </c>
     </row>
@@ -2348,12 +2348,12 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>test_900314_tax_report_request.py:32</t>
+          <t>test_900314_tax_report_request.py:35</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>В том же шаге «Проверить запрос» не проверяется AgreementNumbers: кейс требует номер брокерского договора клиента</t>
+          <t>AgreementNumbers в запросе не проверяется. Комментарий оправдывает это тем, что СОФР берёт номера договоров из своей базы, но кейс требует номер брокерского договора клиента в запросе</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>test_900315_tax_report_ready.py:10, вызов — test_900315_tax_report_ready.py:44</t>
+          <t>test_900315_tax_report_ready.py:10</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -2385,7 +2385,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>…заметил, что между попытками нет паузы, или предложил готовый wait_tax_report_status. Засчитываем и «нагрузка на БД», «тысячи запросов в логе», если причина — повтор без паузы. Отличие от Д315.2: там запрос ищет не ту справку</t>
+          <t>…заметил, что между попытками нет паузы, или предложил готовый wait_tax_report_status. Засчитываем и у вызова в строке 44. Засчитываем и «нагрузка на БД», «тысячи запросов в логе», если причина — повтор без паузы. Отличие от Д315.2: там запрос ищет не ту справку</t>
         </is>
       </c>
     </row>
@@ -2402,7 +2402,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>test_900315_tax_report_ready.py:13, вызов — test_900315_tax_report_ready.py:44</t>
+          <t>test_900315_tax_report_ready.py:13</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -2412,7 +2412,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>…понял, что запрос может вернуть другую справку клиента, и предложил искать по id заявки. Отличие от Д315.1: там нет паузы между попытками</t>
+          <t>…понял, что запрос может вернуть другую справку клиента, или предложил искать по id заявки. Засчитываем и у вызова в строке 44. Отличие от Д315.1: там нет паузы между попытками</t>
         </is>
       </c>
     </row>
@@ -2520,7 +2520,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>…указал, что адрес кабинета зашит, и предложил брать его из настроек стенда (base_url). Засчитываем и падение с ERR_CONNECTION_REFUSED на другом порту, если названа эта причина</t>
+          <t>…указал, что адрес кабинета зашит, или предложил брать его из настроек стенда (base_url). Засчитываем и падение с ERR_CONNECTION_REFUSED на другом порту, если названа эта причина</t>
         </is>
       </c>
     </row>
@@ -2763,7 +2763,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка остатка не ждёт его обновления, и предложил expect(...).to_have_text. Отличие от Д317.4: там пауза</t>
+          <t>…понял, что проверка остатка не ждёт его обновления, или предложил expect(...).to_have_text. Отличие от Д317.4: там пауза</t>
         </is>
       </c>
     </row>
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>test_900318_withdraw_over_balance.py:35</t>
+          <t>test_900318_withdraw_over_balance.py:29</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Новый ожидаемый результат кейса: остаток после отказа — 5 000,00 ₽. Тест его не проверяет и не заметит, если сервис при отказе всё же списал сумму или комиссию</t>
+          <t>Новый ожидаемый результат кейса: остаток после отказа — 5 000,00 ₽. Шаг «Проверить отказ» (строка 29 — его заголовок) его не проверяет и не заметит, если сервис при отказе всё же списал сумму или комиссию</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
@@ -2952,7 +2952,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>…указал, что год зашит, и предложил считать прошлый год от текущей даты. Отличие от Д319.1: там зашит адрес стенда</t>
+          <t>…указал, что год зашит, или предложил считать прошлый год от текущей даты. Отличие от Д319.1: там зашит адрес стенда</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E95" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка не ждёт нужного текста и не повторяется, и предложил expect(...).to_have_text</t>
+          <t>…понял, что проверка не ждёт нужного текста и не повторяется, или предложил expect(...).to_have_text</t>
         </is>
       </c>
     </row>
@@ -3158,12 +3158,12 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>test_900320_change_tariff.py:25</t>
+          <t>test_900320_change_tariff.py:24</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
         <is>
-          <t>Тариф в профиле после смены не проверяется, хотя кейс требует «Трейдер». Страница перерисовывает профиль после смены, и проверить его можно тут же</t>
+          <t>Шаг «Проверить смену тарифа» (строка 24 — его заголовок): тариф в профиле после смены не проверяется, хотя кейс требует «Трейдер». Страница перерисовывает профиль после смены, и проверить его можно тут же</t>
         </is>
       </c>
       <c r="E101" s="2" t="inlineStr">
@@ -3187,7 +3187,12 @@
       </c>
       <c r="E103" s="3" t="inlineStr">
         <is>
-          <t>Ставим 1, если участник предлагает «исправить» это место. Если сам объяснил, почему код верен, — 0. Каждая ловушка −2 балла</t>
+          <t>Ставим 1, если участник считает это место ошибкой. Если сам объяснил, почему код верен, — 0. Каждая ловушка −2 балла</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>Попался (1/0)</t>
         </is>
       </c>
     </row>

--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Имя метода без test_: pytest его не собирает, и тест не запускается ни в одном прогоне</t>
+          <t>Имя метода без test_: pytest не собирает TK900302, и тест не запускается</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -647,17 +647,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:19</t>
+          <t>test_900302_second_iis.py:27</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Код и тело ответа выводятся через print: в отчёт Allure и в лог это не попадает, pytest показывает вывод только у упавших тестов. Отладочный вывод вместо проверки</t>
+          <t>Отладочный print вместо штатного логирования или вложения отчёта; клиент API уже пишет ответ в лог и Allure</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>…указал на отладочный вывод в консоль, или предложил убрать его или заменить логом. Отличие от Д302.3–Д302.5: там речь о самих проверках ответа и БД</t>
+          <t>…указал на оставленный отладочный вывод, или предложил убрать его либо заменить штатным логом</t>
         </is>
       </c>
     </row>
@@ -674,17 +674,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:22</t>
+          <t>test_900302_second_iis.py:30</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>is_not(201) проходит при любом другом ответе — 400, 401, 500: тест не отличает правильный отказ от поломки. Кейс требует 409</t>
+          <t>is_not(201) допускает любой другой код, в том числе 400, 401 и 500, хотя кейс требует 409</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>…предложил проверять именно 409 или указал, что проверка пройдёт при любой ошибке. Отличие от Д302.4 и Д302.5: здесь код ответа проверяется неточно, там проверок нет совсем</t>
+          <t>…предложил проверять именно 409 или объяснил, почему проверки «не 201» недостаточно. Здесь код ответа; Д302.4 — текст, Д302.5 — число ИИС</t>
         </is>
       </c>
     </row>
@@ -701,17 +701,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:23</t>
+          <t>test_900302_second_iis.py:31</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Текст ошибки «У клиента уже есть действующий ИИС» не проверяется. Комментарий оправдывает это тем, что текст на стендах разный, хотя кейс требует именно этот текст</t>
+          <t>В тексте ошибки проверяется только слово «ИИС». Подойдёт и другой отказ с этим словом, хотя кейс задаёт полное сообщение</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>…указал, что текст ошибки не проверен. Отличие от Д302.3: там неточно проверен код ответа. Отличие от Д302.5: там не сделан шаг 2 — проверка в БД</t>
+          <t>…указал на слишком широкую проверку текста или предложил сверять «У клиента уже есть действующий ИИС». Здесь текст, Д302.3 — код ответа</t>
         </is>
       </c>
     </row>
@@ -728,17 +728,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>test_900302_second_iis.py:21</t>
+          <t>test_900302_second_iis.py:36</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2 кейса не сделан: шаг «Проверить, что второй ИИС не открыт» (строка 21 — его заголовок) смотрит только ответ API, а не то, что в БД у клиента по-прежнему один ИИС</t>
+          <t>Число ИИС после отказа проверяется как «больше нуля»: два ИИС тоже пройдут. До запроса был один, и после должен остаться один</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>…указал, что тест не проверяет договоры клиента в БД. Отличие от Д302.3 и Д302.4: те про ответ API на шаге 1</t>
+          <t>…указал, что проверка количества допускает второй ИИС, или предложил сравнивать с 1. Не засчитываем как отсутствие проверки БД: она есть, но неточная</t>
         </is>
       </c>
     </row>
@@ -755,17 +755,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>test_900303_refill.py:18–19, test_900303_refill.py:30–32</t>
+          <t>test_900303_refill.py:29</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Исполнение поручения проверяется по числу исполненных поручений на всём стенде: «стало на одно больше». Это число меняют все, кто работает со стендом. В песочнице клиенты стенда пополняют счета каждую секунду, и тест падает всегда: исполненных поручений становится больше ожидаемого на несколько. Нужно ждать статус своего поручения по id</t>
+          <t>Берётся последнее исполненное поручение всего стенда, без привязки к своему order_id или договору. Чужое пополнение меняет выбранную строку и может уронить проверку id при исправном сервисе</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>…понял, что счётчик общий для стенда и его меняют другие, или объяснил этим постоянное падение TK900303. Засчитываем и «упадёт при параллельном запуске», если причина — общий счётчик. Отличие от Д303.3: там пауза вместо ожидания</t>
+          <t>…указал, что SQL может выбрать чужое поручение, или предложил искать по order_id из ответа. Место дефекта — сам запрос; последующее падение на сравнении id тоже засчитываем с этой причиной</t>
         </is>
       </c>
     </row>
@@ -782,17 +782,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>test_900303_refill.py:24</t>
+          <t>test_900303_refill.py:23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Статус нового поручения может быть NEW или EXECUTED: проверка пройдёт, даже если поручение создано сразу исполненным. Кейс требует NEW</t>
+          <t>Статус нового поручения может быть NEW или EXECUTED: тест примет сразу исполненное поручение, хотя кейс требует NEW</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка допускает не тот статус и не отличает новое поручение. Отличие от Д303.4: там неточно проверен остаток</t>
+          <t>…объяснил, что проверка допускает неверный начальный статус. Д303.3 — пауза, Д303.1 — выбор поручения в БД</t>
         </is>
       </c>
     </row>
@@ -809,17 +809,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>test_900303_refill.py:27</t>
+          <t>test_900303_refill.py:26</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>time.sleep(3) вместо ожидания статуса поручения. В InvestDb для этого есть wait_order_status</t>
+          <t>time.sleep(3) вместо ожидания исполнения своего поручения по условию. В InvestDb есть wait_order_status</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>…предложил ожидание по условию вместо паузы. Отличие от Д303.1: там исполнение проверяется по общему счётчику</t>
+          <t>…предложил ожидание по условию вместо фиксированной паузы. Не объединяем с Д303.1: там запрос выбирает чужую запись</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Остаток по API проверяется подстрокой «10000» — пройдёт и для «110000.00», и для «10000.50»</t>
+          <t>Остаток по API проверяется подстрокой «10000»: пройдут и «110000.00», и «10000.50»</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка части строки пропустит неверный остаток. Отличие от Д303.5: там остаток в БД. Отличие от Д303.2: там статус поручения</t>
+          <t>…объяснил, что подстрока пропустит неверный остаток. Д303.5 — выбор счёта в БД</t>
         </is>
       </c>
     </row>
@@ -863,17 +863,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>test_900303_refill.py:35–36</t>
+          <t>test_900303_refill.py:35</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Остаток в БД читается по договору без условия на валюту: если у договора несколько счетов, запрос вернёт любой. Готовый get_account выбирает рублёвый счёт</t>
+          <t>Счёт выбирается по договору без валюты: при нескольких счетах запрос может вернуть не рублёвый. Готовый get_account выбирает RUB</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>…указал, что запрос не выбирает рублёвый счёт, или предложил готовый метод с валютой. Отличие от Д303.4: там остаток по API</t>
+          <t>…указал на отсутствие валюты в SQL или предложил готовый метод с выбором рублёвого счёта</t>
         </is>
       </c>
     </row>
@@ -971,17 +971,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>test_900304_withdraw_over_balance.py:30–33</t>
+          <t>test_900304_withdraw_over_balance.py:31</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>Условие created_at = date('now') сравнивает дату со временем (2026-10-14 21:05:12) с датой (2026-10-14): строки не равны никогда, запрос всегда возвращает 0. Проверка «поручение не создано» не может упасть</t>
+          <t>В шаге проверки отсутствия вывода SQL считает пополнения (REFILL) вместо выводов (WITHDRAW). Созданное поручение на вывод не попадёт в счётчик</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>…понял, что условие по дате никогда не выполняется и проверка всегда проходит. Отличие от Д304.5: там остаток</t>
+          <t>…указал на неверный тип операции в SQL или предложил WITHDRAW вместо REFILL. Причина теперь видна в строке запроса; знания формата времени не требуется</t>
         </is>
       </c>
     </row>
@@ -1057,7 +1057,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>Тест меняет словарь client_defaults, общий на весь прогон, и не возвращает: все клиенты, созданные после него в том же процессе, — на «Трейдере». С pytest tests/api и в полном прогоне TK900309 падает с «Тариф «Трейдер» уже подключён». TK900311 остаётся зелёным, потому что тариф в событии не проверяется (Д311.5), но в его логе клиент создан с "tariff": "TRADER". TK900320 пропускается с «Клиент уже на «Трейдере»» (Д320.1). Отдельно все три проходят. С -n 4 у каждого воркера свой client_defaults, поэтому страдают только тесты на воркере TK900305. Нужно передать тариф только своему клиенту</t>
+          <t>Тест меняет словарь client_defaults, общий на весь прогон, и не возвращает: все клиенты, созданные после него в том же процессе, — на «Трейдере». С uv run pytest tests/1-api и в полном прогоне TK900309 падает с «Тариф «Трейдер» уже подключён». TK900311 остаётся зелёным, потому что тариф в событии не проверяется (Д311.5), но в его логе клиент создан с "tariff": "TRADER". TK900320 пропускается с «Клиент уже на «Трейдере»» (Д320.1). Отдельно TK900311 и TK900320 проходят. У TK900309 теперь есть собственные ошибки Д309.3 и Д309.5; отдельно он падает по ним, а в полном прогоне — раньше, на ответе 409 из-за Д305.2. С -n 4 у каждого воркера свой client_defaults, поэтому страдают только тесты на воркере TK900305. Нужно передать тариф только своему клиенту</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1511,17 +1511,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>test_900308_close_with_balance.py:35</t>
+          <t>test_900308_close_with_balance.py:37</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: остаток 1 000 после отказа не проверяется</t>
+          <t>Остаток после отказа проверяется как «больше нуля»: 1, 500 и 2 000 тоже пройдут. Кейс требует ровно 1 000</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>…указал, что остаток не проверен. Отличие от Д308.5: там статус договора по API</t>
+          <t>…указал на слишком широкое сравнение остатка или предложил проверять 1 000. Проверка есть, но допускает неверную сумму</t>
         </is>
       </c>
     </row>
@@ -1538,17 +1538,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>test_900308_close_with_balance.py:36</t>
+          <t>test_900308_close_with_balance.py:40</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: договор по API запрашивается, но статус ACTIVE в ответе не проверяется</t>
+          <t>Под названием «Статус договора по API после отказа» проверяется agreement из подготовки. Свежий ответ — agreement_api, а старый словарь не отражает результат операции</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>…указал, что ответ API со статусом договора не проверен. Отличие от Д308.4: там остаток</t>
+          <t>…заметил проверку старого снимка вместо свежего ответа API или предложил agreement_api.json()['status']. Д308.4 — сравнение остатка</t>
         </is>
       </c>
     </row>
@@ -1565,17 +1565,17 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>test_900309_change_tariff.py:14–16</t>
+          <t>test_900309_change_tariff.py:19</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Шаг 1 кейса не сделан: тариф «Инвестор» до смены не проверяется. Если клиент уже на «Трейдере» (так бывает в полном прогоне из-за Д305.2), тест падает на смене тарифа, и по падению не видно, что не выполнено предусловие</t>
+          <t>Проверка тарифа до смены допускает и TRADER, хотя кейс требует INVESTOR. Клиент, который уже на «Трейдере», проходит проверку предусловия</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>…указал, что тариф до смены не проверен. Отличие от Д309.5: там профиль после смены. Отличие от Д305.2: если участник объяснил, почему клиент уже на «Трейдере» (TK900305 меняет client_defaults), — это Д305.2; если в замечании есть и то и другое, засчитываем оба</t>
+          <t>…указал на допустимый TRADER до смены или предложил строго INVESTOR. Если участник также нашёл источник изменённых defaults в TK900305, это отдельно Д305.2</t>
         </is>
       </c>
     </row>
@@ -1592,17 +1592,17 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>test_900309_change_tariff.py:19</t>
+          <t>test_900309_change_tariff.py:24</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>assert_that с одним аргументом: проверяется только, что тариф в ответе не пустой — INVESTOR тоже пройдёт</t>
+          <t>assert_that получает значение без matcher: проверяется лишь непустой тариф, а не равенство TRADER</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>…понял, что тариф в ответе не сравнивается с TRADER и проверка пройдёт при любом тарифе. Отличие от Д309.5: там профиль не проверен совсем</t>
+          <t>…объяснил, что другой непустой тариф пройдёт, или предложил сравнение с TRADER. Д309.5 — другой ответ, профиль после смены</t>
         </is>
       </c>
     </row>
@@ -1619,17 +1619,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>test_900309_change_tariff.py:24–25</t>
+          <t>test_900309_change_tariff.py:29</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Запись истории берётся с LIMIT 1 без сортировки: БД вернёт любую, обычно самую старую. Если клиент менял тариф раньше, проверится не та запись. Готовый get_tariff_history сортирует</t>
+          <t>SQL ищет историю с новым тарифом INVESTOR, хотя выполнена смена на TRADER. Нужная запись не попадёт в результат; у нового клиента запрос вернёт None</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>…понял, что без сортировки запрос возвращает не обязательно последнюю запись</t>
+          <t>…заметил неверный новый тариф в фильтре SQL или предложил получать историю своего клиента без этого фильтра. Здесь выбор записи; Д309.4 — сообщение следующей проверки</t>
         </is>
       </c>
     </row>
@@ -1646,17 +1646,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>test_900309_change_tariff.py:26</t>
+          <t>test_900309_change_tariff.py:31</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Условие собрано в одно булево значение и проверяется is_(True) без сообщения: при падении будет Expected: &lt;True&gt; but: was &lt;False&gt;, и не видно, что в записи истории</t>
+          <t>Два сравнения сведены в True/False без сообщения: при падении не видно, какое поле истории неверно и что вернула БД</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>…указал, что по падению не понять, что в истории, или предложил проверку по полям записи или сообщение</t>
+          <t>…указал на неинформативное падение или предложил проверки по полям либо сообщение с содержимым записи</t>
         </is>
       </c>
     </row>
@@ -1673,17 +1673,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>test_900309_change_tariff.py:27</t>
+          <t>test_900309_change_tariff.py:34</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Профиль после смены запрашивается, но тариф TRADER в нём не проверяется</t>
+          <t>После смены тариф в профиле сравнивается со старым значением из profile_before. Правильный переход INVESTOR → TRADER уронит тест; ожидается TRADER</t>
         </is>
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>…указал, что ответ с профилем не проверен. Отличие от Д309.1: там тариф до смены. Отличие от Д309.2: там неточно проверен ответ на смену тарифа</t>
+          <t>…заметил сравнение с тарифом до смены или предложил ожидать TRADER в свежем профиле. Д309.1 — проверка до операции</t>
         </is>
       </c>
     </row>
@@ -1700,17 +1700,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:7</t>
+          <t>test_900310_login_lock.py:11</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Пароль клиента стенда — константа в коде</t>
+          <t>xfail без strict=True: правильный прогон будет XPASS, падение — XFAIL; ни один исход не делает прогон красным</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>…указал на пароль клиента в коде. Отличие от Д310.2: здесь секрет в коде, там тест ломает общего клиента. Замечание только «нужен свой клиент вместо клиента стенда» засчитываем как Д310.2</t>
+          <t>…объяснил маскировку падений пометкой или смысл XPASS без строгого режима. Само наличие XPASS без причины недостаточно</t>
         </is>
       </c>
     </row>
@@ -1727,17 +1727,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:6, test_900310_login_lock.py:36</t>
+          <t>test_900310_login_lock.py:23</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Тест блокирует общего клиента стенда и не разблокирует: после прогона под ним никто не войдёт, пока тест не запустят снова. Свой клиент из фикстуры client решает и это, и Д310.1, и Д310.4</t>
+          <t>На неверный пароль ожидается любой код кроме 200: 400, 403 и 500 тоже пройдут. Кейс требует 401 на каждой из трёх попыток</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>…понял, что тест оставляет клиента стенда заблокированным, или предложил работать со своим клиентом вместо общего. Общее замечание «нужен свой клиент», «тест зависит от клиента стенда» засчитываем только как Д310.2. Отличие от Д310.1: там пароль в коде. Отличие от Д310.4: там запись в БД сервиса перед тестом</t>
+          <t>…указал на слишком широкую проверку кода или предложил строго 401. Цикл из трёх попыток корректен и не является этим дефектом</t>
         </is>
       </c>
     </row>
@@ -1754,17 +1754,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:14</t>
+          <t>test_900310_login_lock.py:28</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>xfail без strict=True: прошедший тест — XPASS, упавший — XFAIL, прогон зелёный в обоих случаях. Тест не может упасть ни при каком поведении сервиса</t>
+          <t>В шаге «Войти с верным паролем» снова отправляется wrong-password. Вход с настоящим паролем после блокировки не проверяется</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>…понял, что пометка «ожидаемое падение» без строгого режима делает результат теста безразличным, или назвал XPASS у TK900310 и объяснил, что прогон его не считает. Засчитываем и формулировку по пункту 5</t>
+          <t>…заметил неверный пароль именно в шаге после трёх попыток или предложил client['password']. Три предыдущих неверных пароля нужны по кейсу</t>
         </is>
       </c>
     </row>
@@ -1781,17 +1781,17 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:18–19</t>
+          <t>test_900310_login_lock.py:31</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Перед тестом блокировка снимается прямым UPDATE в БД сервиса — в обход сервиса и в чужих данных. Параллельный прогон того же теста или коллега, который проверяет блокировку этого клиента, получит разблокированного клиента посреди своего сценария</t>
+          <t>Для отказа заблокированному клиенту проверяется только слово «заблокирована», хотя кейс требует полное сообщение с обращением в поддержку</t>
         </is>
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>…указал, что перед тестом состояние клиента сбрасывается записью в БД сервиса в обход API. Замечание только о том, что тест работает с общим клиентом или меняет его данные, без слов о записи в БД, — это Д310.2. Отличие от Д310.1: там пароль в коде</t>
+          <t>…указал на неполное сравнение текста или предложил полное сообщение. Д310.2 — коды первых трёх ответов</t>
         </is>
       </c>
     </row>
@@ -1808,17 +1808,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:35</t>
+          <t>test_900310_login_lock.py:34</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Логин подставляется в SQL через f-строку, а не параметром: логин с апострофом сломает запрос, а значение извне — путь к SQL-инъекции. В InvestDb есть get_client_by_login с параметром</t>
+          <t>SQL выбирает любого заблокированного клиента без привязки к клиенту теста. Найденный статус заведомо LOCKED; чужая блокировка может скрыть неверное состояние своего клиента</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>…предложил параметр запроса или готовый метод вместо подстановки в строку</t>
+          <t>…указал на отсутствие фильтра по своему клиенту, выбор произвольной заблокированной записи или заведомый LOCKED из условия запроса</t>
         </is>
       </c>
     </row>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>Адрес кабинета http://localhost:18300/cabinet/ зашит, хотя base_url настроен в tests/ui/conftest.py, а фикстура cabinet открывает относительный путь /cabinet/. На другом стенде тест пойдёт в песочницу на 18300. С INVEST_SANDBOX_PORT=18301 pytest tests/ui он падает с ERR_CONNECTION_REFUSED</t>
+          <t>Адрес кабинета http://localhost:18300/cabinet/ зашит, хотя base_url настроен в tests/3-ui/conftest.py, а фикстура cabinet открывает относительный путь /cabinet/. На другом стенде тест пойдёт в песочницу на 18300. С INVEST_SANDBOX_PORT=18301 pytest tests/3-ui он падает с ERR_CONNECTION_REFUSED</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
-          <t>Фикстура browser_context_args в модуле теста подменяет адрес стенда на зашитый http://localhost:18300. Настройка base_url из tests/ui/conftest.py для этого теста не действует: на другом стенде тест, вместе со входом в фикстуре cabinet, пойдёт в песочницу на 18300. С INVEST_SANDBOX_PORT=18301 pytest tests/ui — ERROR в подготовке, ERR_CONNECTION_REFUSED</t>
+          <t>Фикстура browser_context_args в модуле теста подменяет адрес стенда на зашитый http://localhost:18300. Настройка base_url из tests/3-ui/conftest.py для этого теста не действует: на другом стенде тест, вместе со входом в фикстуре cabinet, пойдёт в песочницу на 18300. С INVEST_SANDBOX_PORT=18301 pytest tests/3-ui — ERROR в подготовке, ERR_CONNECTION_REFUSED</t>
         </is>
       </c>
       <c r="E92" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="D104" s="2" t="inlineStr">
         <is>
-          <t>Это константа в тексте запроса, а не значение извне: тесты проверяют рублёвый счёт договора. Параметр здесь не нужен. В Д310.5 в запрос подставляется значение — там ошибка. В Д303.5 условия на валюту нет вовсе — там тоже ошибка</t>
+          <t>Это константа в тексте запроса, а не значение извне: тесты проверяют рублёвый счёт договора. Параметр здесь не нужен. В Д303.5 условия на валюту нет вовсе — там тоже ошибка</t>
         </is>
       </c>
       <c r="E104" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       <c r="B109" s="2" t="inlineStr"/>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>test_900310_login_lock.py:22–26</t>
+          <t>test_900310_login_lock.py:21</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
         <is>
-          <t>Цикл — три одинаковые попытки входа из кейса, номер попытки есть в сообщении проверки. Замечание о клиенте стенда в строке 23 относится к Д310.1 или Д310.2, а не к циклу</t>
+          <t>Цикл выполняет ровно три одинаковые попытки по кейсу. Сам цикл корректен; замечания к коду ответа внутри него — Д310.2, а не попадание в ловушку</t>
         </is>
       </c>
       <c r="E109" s="2" t="inlineStr">

--- a/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
+++ b/review-tasks/1d-python-review/jury/scoring-sheet.xlsx
@@ -2105,7 +2105,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:6, test_900313_duplicate_payment.py:19</t>
+          <t>test_900313_duplicate_payment.py:6</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -2159,17 +2159,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:24, test_900313_duplicate_payment.py:27</t>
+          <t>test_900313_duplicate_payment.py:25–26</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Проверки стоят сразу после повторной отправки. Сервис читает топик раз в полсекунду и ещё не успел обработать дубль, поэтому остаток 1 000 и одно поручение будут, даже если защиты от повторов нет. Проверка не может упасть. Нужно дождаться, пока сервис обработает повтор: например, следом отправить контрольное поступление с новым PaymentId и дождаться его события — сообщения одного договора обрабатываются по порядку</t>
+          <t>После повторной отправки ожидается любое событие EXECUTED своего договора. Под условие подходит событие первого зачисления: ожидание сразу заканчивается и не подтверждает обработку дубля. Проверки остатка и числа поручений могут пройти до повторного зачисления даже без защиты от дублей. Нужно дождаться, пока сервис обработает повтор: например, следом отправить контрольное поступление с новым PaymentId и дождаться его события — сообщения одного договора обрабатываются по порядку</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>…понял, что проверка выполняется до обработки повторного сообщения. Способ дождаться обработки называть не обязательно. Отличие от Д313.2: там не проверен шаг 1. Отличие от Д313.4: там нет проверки топика</t>
+          <t>…понял, что ожидание находит старое событие первого платежа и не подтверждает обработку повтора, или что последующие проверки выполняются до обработки дубля. Способ дождаться обработки называть не обязательно. Отличие от Д313.2: там не проверен шаг 1. Отличие от Д313.4: там нет проверки топика</t>
         </is>
       </c>
     </row>
@@ -2186,12 +2186,12 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:26</t>
+          <t>test_900313_duplicate_payment.py:28</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>Шаг 3 (строка 26 — заголовок шага проверки): не проверено, что в топике invest.money-orders по договору одно событие EXECUTED на 1 000 ₽. Если дубль зачислится второй раз, другие системы получат второе событие о зачислении</t>
+          <t>Шаг 3 (строка 28 — заголовок шага проверки): не проверено, что в топике invest.money-orders по договору одно событие EXECUTED на 1 000 ₽. Если дубль зачислится второй раз, другие системы получат второе событие о зачислении</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
@@ -2213,7 +2213,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>test_900313_duplicate_payment.py:28</t>
+          <t>test_900313_duplicate_payment.py:30</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>Шаг 2: тип договора «Брокерский договор» не проверяется — в строке проверен только остаток. Кейс требует и тип</t>
+          <t>Ячейка типа договора проверяется только на непустоту: «ИИС» тоже пройдёт, хотя кейс требует «Брокерский договор». Проверка остатка ниже тип договора не подтверждает</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>…указал, что тип договора в списке не проверен. Отличие от Д316.4: там строка берётся по позиции. Отличие от Д316.3: там ФИО в шапке</t>
+          <t>…указал, что непустая ячейка не подтверждает тип «Брокерский договор», или предложил проверить точный тип. Отличие от Д316.4: там строка берётся по позиции. Отличие от Д316.3: там ФИО в шапке</t>
         </is>
       </c>
     </row>
@@ -2645,17 +2645,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>test_900317_refill.py:18–20</t>
+          <t>test_900317_refill.py:20</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>Поручение создаётся вручную, и кнопка «Создать поручение» нажимается с force=True. Так Playwright пропускает проверки перед кликом: видна ли кнопка, доступна ли она, не перекрыта ли другим элементом. Тест не поймает ошибку вёрстки, из-за которой пользователь не смог бы нажать кнопку. Шаги к тому же повторяют готовый agreement_page.refill(10000)</t>
+          <t>Кнопка «Создать поручение» нажимается с force=True: клик обходит часть проверок доступности действия, в том числе проверку, что кнопка получает события указателя. Тест может пройти, даже если кнопку перекрывает другой элемент и пользователь нажать её не может. Ручные шаги создания поручения сами по себе корректны</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>…указал, что force=True отключает проверки перед кликом и прячет ошибки интерфейса, или предложил готовый refill вместо ручных шагов</t>
+          <t>…указал, что принудительный клик может скрыть недоступность кнопки для пользователя. Предложение готового refill засчитываем, если объяснена проблема force=True; ручные шаги сами по себе дефектом не считаем</t>
         </is>
       </c>
     </row>
@@ -2807,7 +2807,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>test_900318_withdraw_over_balance.py:30–33</t>
+          <t>test_900318_withdraw_over_balance.py:31–34</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>test_900318_withdraw_over_balance.py:34</t>
+          <t>test_900318_withdraw_over_balance.py:35</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>test_900318_withdraw_over_balance.py:35</t>
+          <t>test_900318_withdraw_over_balance.py:36</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -2888,12 +2888,12 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>test_900318_withdraw_over_balance.py:29</t>
+          <t>test_900318_withdraw_over_balance.py:30</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
-          <t>Новый ожидаемый результат кейса: остаток после отказа — 5 000,00 ₽. Шаг «Проверить отказ» (строка 29 — его заголовок) его не проверяет и не заметит, если сервис при отказе всё же списал сумму или комиссию</t>
+          <t>Кейс требует остаток после отказа 5 000,00 ₽. Комментарий «Остаток повторно не проверяем: при отказе он не меняется» заменяет проверку предположением. Тест не заметит, если сервис при отказе всё же списал сумму или комиссию</t>
         </is>
       </c>
       <c r="E91" s="2" t="inlineStr">
